--- a/Arquivos/nao_atualizaveis/Ativo_Propag Três Rios/STATUS - CANDIDATOS PARA TÉCNICO PROPAG 2026.2 (concomitante).xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_Propag Três Rios/STATUS - CANDIDATOS PARA TÉCNICO PROPAG 2026.2 (concomitante).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingrid.chaves\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.20\ddmrj-dados\Planejamento\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_Propag Três Rios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C1ACD-27D1-4B56-830B-7D4316EB29CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B421C9B-3BF5-4621-B0B9-53EE6051570F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -3273,7 +3273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -3309,7 +3309,6 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10486,7 +10485,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10487196-CD69-4BF8-BE93-A7FC752F1565}" name="Tabela dinâmica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTIVO DO NÃO INTERESSE">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10487196-CD69-4BF8-BE93-A7FC752F1565}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTIVO DO NÃO INTERESSE">
   <location ref="B16:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="44">
     <pivotField showAll="0"/>
@@ -10615,7 +10614,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB50CD4C-9273-4D9D-9950-673C5424D1FD}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB50CD4C-9273-4D9D-9950-673C5424D1FD}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
   <location ref="B3:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="44">
     <pivotField showAll="0"/>
@@ -10942,19 +10941,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D6DF00-20D2-4686-964F-B6CE5C54987E}">
   <dimension ref="B2:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>1041</v>
       </c>
       <c r="C2" s="14"/>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>1022</v>
       </c>
@@ -10962,7 +10961,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>1031</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>1026</v>
       </c>
@@ -10978,7 +10977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>1027</v>
       </c>
@@ -10986,7 +10985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>1028</v>
       </c>
@@ -10994,7 +10993,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>1032</v>
       </c>
@@ -11002,7 +11001,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>1024</v>
       </c>
@@ -11010,7 +11009,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>1039</v>
       </c>
@@ -11018,7 +11017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>1025</v>
       </c>
@@ -11026,7 +11025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>1040</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>1029</v>
       </c>
@@ -11042,7 +11041,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>39</v>
       </c>
@@ -11050,59 +11049,59 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>1037</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
         <v>1035</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>1033</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>1036</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
         <v>1038</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
         <v>1029</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23">
         <v>21</v>
       </c>
     </row>
@@ -11117,51 +11116,51 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AQ156"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" customWidth="1"/>
-    <col min="24" max="24" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.33203125" customWidth="1"/>
-    <col min="30" max="30" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.5546875" customWidth="1"/>
-    <col min="40" max="40" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" customWidth="1"/>
+    <col min="24" max="24" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.28515625" customWidth="1"/>
+    <col min="30" max="30" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" customWidth="1"/>
+    <col min="40" max="40" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11292,7 +11291,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>3</v>
       </c>
@@ -11391,7 +11390,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>3</v>
       </c>
@@ -11492,7 +11491,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -11589,7 +11588,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -11686,7 +11685,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -11783,7 +11782,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -11979,7 +11978,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -12074,7 +12073,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -12171,7 +12170,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>3</v>
       </c>
@@ -12270,7 +12269,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>3</v>
       </c>
@@ -12367,7 +12366,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -12466,7 +12465,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>3</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>3</v>
       </c>
@@ -12660,7 +12659,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -12757,7 +12756,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>3</v>
       </c>
@@ -12852,7 +12851,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>3</v>
       </c>
@@ -12949,7 +12948,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>3</v>
       </c>
@@ -13050,7 +13049,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>3</v>
       </c>
@@ -13147,7 +13146,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -13242,7 +13241,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>3</v>
       </c>
@@ -13341,7 +13340,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>3</v>
       </c>
@@ -13444,7 +13443,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>3</v>
       </c>
@@ -13543,7 +13542,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>3</v>
       </c>
@@ -13640,7 +13639,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>3</v>
       </c>
@@ -13741,7 +13740,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -13840,7 +13839,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>3</v>
       </c>
@@ -13937,7 +13936,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="29" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>3</v>
       </c>
@@ -14036,7 +14035,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>3</v>
       </c>
@@ -14133,7 +14132,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="31" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>3</v>
       </c>
@@ -14232,7 +14231,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="32" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>3</v>
       </c>
@@ -14329,7 +14328,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>3</v>
       </c>
@@ -14428,7 +14427,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>3</v>
       </c>
@@ -14527,7 +14526,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>3</v>
       </c>
@@ -14612,7 +14611,7 @@
         <v>49</v>
       </c>
       <c r="AN35" s="4" t="s">
-        <v>1035</v>
+        <v>316</v>
       </c>
       <c r="AO35" s="12">
         <v>46294.50372685185</v>
@@ -14624,7 +14623,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>3</v>
       </c>
@@ -14721,7 +14720,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>3</v>
       </c>
@@ -14820,7 +14819,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>3</v>
       </c>
@@ -14921,7 +14920,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>3</v>
       </c>
@@ -15018,7 +15017,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>3</v>
       </c>
@@ -15117,7 +15116,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>3</v>
       </c>
@@ -15214,7 +15213,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="42" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>3</v>
       </c>
@@ -15313,7 +15312,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -15410,7 +15409,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>3</v>
       </c>
@@ -15507,7 +15506,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>3</v>
       </c>
@@ -15602,7 +15601,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>3</v>
       </c>
@@ -15697,7 +15696,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>3</v>
       </c>
@@ -15794,7 +15793,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>3</v>
       </c>
@@ -15889,7 +15888,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="49" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>3</v>
       </c>
@@ -15988,7 +15987,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>3</v>
       </c>
@@ -16085,7 +16084,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>3</v>
       </c>
@@ -16186,7 +16185,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="52" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>3</v>
       </c>
@@ -16285,7 +16284,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="53" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>3</v>
       </c>
@@ -16380,7 +16379,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>3</v>
       </c>
@@ -16477,7 +16476,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>3</v>
       </c>
@@ -16574,7 +16573,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>3</v>
       </c>
@@ -16673,7 +16672,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>3</v>
       </c>
@@ -16770,7 +16769,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>3</v>
       </c>
@@ -16865,7 +16864,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>3</v>
       </c>
@@ -16962,7 +16961,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>3</v>
       </c>
@@ -17059,7 +17058,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>3</v>
       </c>
@@ -17158,7 +17157,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="62" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>3</v>
       </c>
@@ -17257,7 +17256,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="63" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>3</v>
       </c>
@@ -17354,7 +17353,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="64" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>3</v>
       </c>
@@ -17453,7 +17452,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="65" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>3</v>
       </c>
@@ -17550,7 +17549,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="66" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>3</v>
       </c>
@@ -17649,7 +17648,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="67" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>3</v>
       </c>
@@ -17746,7 +17745,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="68" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>3</v>
       </c>
@@ -17841,7 +17840,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="69" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>3</v>
       </c>
@@ -17938,7 +17937,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="70" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>3</v>
       </c>
@@ -18035,7 +18034,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="71" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>3</v>
       </c>
@@ -18132,7 +18131,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="72" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>3</v>
       </c>
@@ -18231,7 +18230,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="73" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>3</v>
       </c>
@@ -18330,7 +18329,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="74" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>3</v>
       </c>
@@ -18431,7 +18430,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="75" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>3</v>
       </c>
@@ -18532,7 +18531,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="76" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>3</v>
       </c>
@@ -18629,7 +18628,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="77" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>3</v>
       </c>
@@ -18726,7 +18725,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="78" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>3</v>
       </c>
@@ -18825,7 +18824,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="79" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>3</v>
       </c>
@@ -18924,7 +18923,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="80" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>3</v>
       </c>
@@ -19021,7 +19020,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="81" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>3</v>
       </c>
@@ -19120,7 +19119,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="82" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>3</v>
       </c>
@@ -19221,7 +19220,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="83" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>3</v>
       </c>
@@ -19318,7 +19317,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="84" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -19415,7 +19414,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="85" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>3</v>
       </c>
@@ -19514,7 +19513,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="86" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>3</v>
       </c>
@@ -19611,7 +19610,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="87" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>3</v>
       </c>
@@ -19708,7 +19707,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="88" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>3</v>
       </c>
@@ -19805,7 +19804,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="89" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>3</v>
       </c>
@@ -19902,7 +19901,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="90" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>3</v>
       </c>
@@ -19999,7 +19998,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="91" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>3</v>
       </c>
@@ -20098,7 +20097,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="92" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>3</v>
       </c>
@@ -20195,7 +20194,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="93" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>3</v>
       </c>
@@ -20296,7 +20295,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="94" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>3</v>
       </c>
@@ -20393,7 +20392,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="95" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>3</v>
       </c>
@@ -20496,7 +20495,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="96" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>3</v>
       </c>
@@ -20591,7 +20590,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="97" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>3</v>
       </c>
@@ -20690,7 +20689,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="98" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>3</v>
       </c>
@@ -20789,7 +20788,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="99" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>3</v>
       </c>
@@ -20888,7 +20887,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="100" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>3</v>
       </c>
@@ -20987,7 +20986,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="101" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>3</v>
       </c>
@@ -21082,7 +21081,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="102" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>3</v>
       </c>
@@ -21179,7 +21178,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="103" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>3</v>
       </c>
@@ -21276,7 +21275,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="104" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>3</v>
       </c>
@@ -21375,7 +21374,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="105" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>3</v>
       </c>
@@ -21476,7 +21475,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="106" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>3</v>
       </c>
@@ -21577,7 +21576,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="107" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>3</v>
       </c>
@@ -21674,7 +21673,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="108" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>3</v>
       </c>
@@ -21771,7 +21770,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="109" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>3</v>
       </c>
@@ -21868,7 +21867,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="110" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>3</v>
       </c>
@@ -21967,7 +21966,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="111" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>3</v>
       </c>
@@ -22064,7 +22063,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="112" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>3</v>
       </c>
@@ -22163,7 +22162,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="113" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>3</v>
       </c>
@@ -22262,7 +22261,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="114" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>3</v>
       </c>
@@ -22359,7 +22358,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="115" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>3</v>
       </c>
@@ -22454,7 +22453,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="116" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>3</v>
       </c>
@@ -22553,7 +22552,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="117" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>3</v>
       </c>
@@ -22652,7 +22651,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="118" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>3</v>
       </c>
@@ -22749,7 +22748,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="119" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>3</v>
       </c>
@@ -22848,7 +22847,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="120" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>3</v>
       </c>
@@ -22947,7 +22946,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="121" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>3</v>
       </c>
@@ -23046,7 +23045,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="122" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>3</v>
       </c>
@@ -23143,7 +23142,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="123" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>3</v>
       </c>
@@ -23242,7 +23241,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="124" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>3</v>
       </c>
@@ -23341,7 +23340,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="125" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>3</v>
       </c>
@@ -23438,7 +23437,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="126" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>3</v>
       </c>
@@ -23539,7 +23538,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="127" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>3</v>
       </c>
@@ -23636,7 +23635,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="128" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>3</v>
       </c>
@@ -23737,7 +23736,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="129" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>3</v>
       </c>
@@ -23836,7 +23835,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="130" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>3</v>
       </c>
@@ -23937,7 +23936,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="131" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>3</v>
       </c>
@@ -24036,7 +24035,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="132" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>3</v>
       </c>
@@ -24135,7 +24134,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="133" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>3</v>
       </c>
@@ -24232,7 +24231,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="134" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>3</v>
       </c>
@@ -24329,7 +24328,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="135" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>3</v>
       </c>
@@ -24424,7 +24423,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="136" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>3</v>
       </c>
@@ -24523,7 +24522,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="137" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>3</v>
       </c>
@@ -24618,7 +24617,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="138" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>3</v>
       </c>
@@ -24713,7 +24712,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="139" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>3</v>
       </c>
@@ -24812,7 +24811,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="140" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>3</v>
       </c>
@@ -24909,7 +24908,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="141" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>3</v>
       </c>
@@ -25006,7 +25005,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="142" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>3</v>
       </c>
@@ -25103,7 +25102,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="143" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>3</v>
       </c>
@@ -25202,7 +25201,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="144" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>3</v>
       </c>
@@ -25301,7 +25300,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="145" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>3</v>
       </c>
@@ -25398,7 +25397,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="146" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>3</v>
       </c>
@@ -25497,7 +25496,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="147" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>3</v>
       </c>
@@ -25592,7 +25591,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="148" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>3</v>
       </c>
@@ -25689,7 +25688,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="149" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>3</v>
       </c>
@@ -25788,7 +25787,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="150" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>3</v>
       </c>
@@ -25887,7 +25886,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="151" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>3</v>
       </c>
@@ -25986,7 +25985,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="152" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>3</v>
       </c>
@@ -26081,7 +26080,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="153" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>3</v>
       </c>
@@ -26180,7 +26179,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="154" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>3</v>
       </c>
@@ -26275,7 +26274,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="155" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>3</v>
       </c>
@@ -26372,7 +26371,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="156" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:43" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>3</v>
       </c>
